--- a/nodes_source_analyses/energy/energy/energy_production_fischer_tropsch_synthetic_must_run.xlsx
+++ b/nodes_source_analyses/energy/energy/energy_production_fischer_tropsch_synthetic_must_run.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathijsbijkerk/Github/etdataset/nodes_source_analyses/energy/energy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyradehaan/github/etdataset/nodes_source_analyses/energy/energy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75722749-92A2-9F4E-8AD1-53D4446AF03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FD31C7-AD71-4A41-92C1-9B1CCD940B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11700" yWindow="-28300" windowWidth="51200" windowHeight="27320" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5740" yWindow="-21600" windowWidth="38400" windowHeight="21600" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="220">
   <si>
     <t>Source</t>
   </si>
@@ -759,21 +759,12 @@
     <t>t CO2/t FT liquids</t>
   </si>
   <si>
-    <t>CO2 consumption per t kerosene</t>
-  </si>
-  <si>
-    <t>t CO2/t kerosene</t>
-  </si>
-  <si>
     <t>LHV kerosene</t>
   </si>
   <si>
     <t>MJ/kg</t>
   </si>
   <si>
-    <t>CO2 consumption per MJ kerosene</t>
-  </si>
-  <si>
     <t>kg CO2/MJ kerosene</t>
   </si>
   <si>
@@ -781,13 +772,46 @@
   </si>
   <si>
     <t>No data available, assumed to be part of initial investment</t>
+  </si>
+  <si>
+    <t>co2_utilisation_per_mj</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ</t>
+  </si>
+  <si>
+    <t>assumption: all output is kerosene</t>
+  </si>
+  <si>
+    <t>CO2 consumption per MJ product</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ FT products</t>
+  </si>
+  <si>
+    <t>Emission factor gasoline</t>
+  </si>
+  <si>
+    <t>Emissions factor kerosene</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ gasoline</t>
+  </si>
+  <si>
+    <t>check with emissions factors (EF) to confirm required input of CO2 is higher than EF</t>
+  </si>
+  <si>
+    <t>copied from carriers.csv nl2023</t>
+  </si>
+  <si>
+    <t>CO2 utilisation per MJ product output</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -795,13 +819,21 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="169" formatCode="[$-413]mmm\-yy;@"/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Lettertype hoofdtekst"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1409,899 +1441,901 @@
   </borders>
   <cellStyleXfs count="500">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="39" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="39" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="38" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="35" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="39" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="33" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="41" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="40" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="9" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="40" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="38" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="38" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="32" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="39" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="22" fillId="2" borderId="0" xfId="499" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="0" xfId="499" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="497" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="499" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="23" fillId="2" borderId="0" xfId="499" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="497" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="2" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="2" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="500">
     <cellStyle name="Comma" xfId="499" builtinId="3"/>
@@ -3495,7 +3529,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A2:K45"/>
+  <dimension ref="A2:K46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="2" width="3.5" style="29" customWidth="1"/>
@@ -3510,30 +3544,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="195" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196"/>
+      <c r="C2" s="196"/>
+      <c r="D2" s="196"/>
+      <c r="E2" s="197"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="B3" s="197"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="199"/>
+      <c r="E3" s="200"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="197"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="199"/>
+      <c r="B4" s="198"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="200"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="200"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="202"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="203"/>
     </row>
     <row r="7" spans="1:11" ht="17" thickBot="1"/>
     <row r="8" spans="1:11">
@@ -3850,8 +3884,8 @@
         <v>60</v>
       </c>
       <c r="H26" s="82"/>
-      <c r="I26" s="207" t="s">
-        <v>211</v>
+      <c r="I26" s="194" t="s">
+        <v>208</v>
       </c>
       <c r="J26" s="83"/>
     </row>
@@ -3869,8 +3903,8 @@
         <v>61</v>
       </c>
       <c r="H27" s="82"/>
-      <c r="I27" s="207" t="s">
-        <v>211</v>
+      <c r="I27" s="194" t="s">
+        <v>208</v>
       </c>
       <c r="J27" s="83"/>
     </row>
@@ -4009,27 +4043,38 @@
     </row>
     <row r="35" spans="1:10" ht="17" thickBot="1">
       <c r="A35" s="71"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="78"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="B35" s="72"/>
+      <c r="C35" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="209">
+        <f>ROUND(Notes!F48,5)</f>
+        <v>9.0380000000000002E-2</v>
+      </c>
+      <c r="F35" s="70"/>
+      <c r="G35" s="208" t="s">
+        <v>219</v>
+      </c>
+      <c r="H35" s="70"/>
+      <c r="I35" s="88" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="73"/>
+    </row>
+    <row r="36" spans="1:10" ht="17" thickBot="1">
       <c r="A36" s="71"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="78"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="71"/>
@@ -4058,6 +4103,8 @@
     <row r="39" spans="1:10">
       <c r="A39" s="71"/>
       <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
       <c r="E39" s="71"/>
       <c r="F39" s="71"/>
       <c r="G39" s="71"/>
@@ -4068,8 +4115,6 @@
     <row r="40" spans="1:10">
       <c r="A40" s="71"/>
       <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
       <c r="E40" s="71"/>
       <c r="F40" s="71"/>
       <c r="G40" s="71"/>
@@ -4115,9 +4160,21 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="71"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="71"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4276,7 +4333,7 @@
       <c r="B13" s="38"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="27" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I7" r:id="rId1" xr:uid="{877979D8-94D4-4246-B8F7-7FF5F6E32CF4}"/>
     <hyperlink ref="I8" r:id="rId2" xr:uid="{06CFC551-C46B-2F44-A4BE-28617D395B80}"/>
@@ -4297,7 +4354,7 @@
     <col min="1" max="2" width="3.5" style="42" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="42" customWidth="1"/>
     <col min="4" max="4" width="7.1640625" style="42" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="42" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" style="42" customWidth="1"/>
     <col min="6" max="6" width="15" style="42" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" style="42" customWidth="1"/>
     <col min="8" max="13" width="10.83203125" style="42"/>
@@ -4388,18 +4445,18 @@
         <v>80</v>
       </c>
       <c r="P6" s="109"/>
-      <c r="Q6" s="205" t="s">
+      <c r="Q6" s="206" t="s">
         <v>111</v>
       </c>
-      <c r="R6" s="206"/>
-      <c r="S6" s="206"/>
-      <c r="T6" s="206"/>
-      <c r="U6" s="206"/>
-      <c r="V6" s="206"/>
-      <c r="W6" s="206"/>
-      <c r="X6" s="206"/>
-      <c r="Y6" s="206"/>
-      <c r="Z6" s="206"/>
+      <c r="R6" s="207"/>
+      <c r="S6" s="207"/>
+      <c r="T6" s="207"/>
+      <c r="U6" s="207"/>
+      <c r="V6" s="207"/>
+      <c r="W6" s="207"/>
+      <c r="X6" s="207"/>
+      <c r="Y6" s="207"/>
+      <c r="Z6" s="207"/>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="46"/>
@@ -4409,7 +4466,7 @@
         <v>72</v>
       </c>
       <c r="F7" s="120">
-        <f>F55</f>
+        <f>F56</f>
         <v>8000</v>
       </c>
       <c r="G7" s="42" t="s">
@@ -4460,7 +4517,7 @@
         <v>73</v>
       </c>
       <c r="F8" s="120">
-        <f>F56</f>
+        <f>F57</f>
         <v>25</v>
       </c>
       <c r="G8" s="42" t="s">
@@ -4508,7 +4565,7 @@
         <v>177</v>
       </c>
       <c r="F9" s="120">
-        <f>F57</f>
+        <f>F58</f>
         <v>2</v>
       </c>
       <c r="G9" s="42" t="s">
@@ -4538,7 +4595,7 @@
         <v>178</v>
       </c>
       <c r="F10" s="104">
-        <f>F58</f>
+        <f>F59</f>
         <v>0.94230769230769229</v>
       </c>
       <c r="O10" s="115" t="s">
@@ -4601,7 +4658,7 @@
         <v>69</v>
       </c>
       <c r="F12" s="184">
-        <f>F60</f>
+        <f>F61</f>
         <v>871988000</v>
       </c>
       <c r="G12" s="42" t="s">
@@ -4649,7 +4706,7 @@
         <v>165</v>
       </c>
       <c r="F13" s="185">
-        <f>F61</f>
+        <f>F62</f>
         <v>2214849.5199999996</v>
       </c>
       <c r="G13" s="42" t="s">
@@ -4677,7 +4734,7 @@
         <v>167</v>
       </c>
       <c r="F14" s="104">
-        <f>F63</f>
+        <f>F64</f>
         <v>91.558739999999986</v>
       </c>
       <c r="G14" s="42" t="s">
@@ -5744,6 +5801,9 @@
       <c r="G46" s="42" t="s">
         <v>203</v>
       </c>
+      <c r="H46" s="42" t="s">
+        <v>211</v>
+      </c>
       <c r="O46" s="178"/>
       <c r="P46" s="178" t="s">
         <v>142</v>
@@ -5764,11 +5824,13 @@
         <v>204</v>
       </c>
       <c r="F47" s="42">
-        <f>F46*H39/H42</f>
-        <v>2.9249999999999998</v>
+        <v>43.15</v>
       </c>
       <c r="G47" s="42" t="s">
         <v>205</v>
+      </c>
+      <c r="H47" s="42" t="s">
+        <v>207</v>
       </c>
       <c r="O47" s="178"/>
       <c r="P47" s="178" t="s">
@@ -5787,16 +5849,17 @@
     </row>
     <row r="48" spans="1:26">
       <c r="E48" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="F48" s="42">
-        <v>43.15</v>
+        <v>212</v>
+      </c>
+      <c r="F48" s="193">
+        <f>F46/F47</f>
+        <v>9.0382387022016217E-2</v>
       </c>
       <c r="G48" s="42" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H48" s="42" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O48" s="178"/>
       <c r="P48" s="178" t="s">
@@ -5815,14 +5878,16 @@
     </row>
     <row r="49" spans="5:26">
       <c r="E49" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F49" s="193">
-        <f>F47/F48</f>
-        <v>6.7786790266512159E-2</v>
+        <v>215</v>
+      </c>
+      <c r="F49" s="42">
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>209</v>
+        <v>206</v>
+      </c>
+      <c r="H49" s="42" t="s">
+        <v>218</v>
       </c>
       <c r="O49" s="178"/>
       <c r="P49" s="178" t="s">
@@ -5840,6 +5905,18 @@
       <c r="Z49" s="117"/>
     </row>
     <row r="50" spans="5:26">
+      <c r="E50" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="F50" s="42">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="G50" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="H50" s="42" t="s">
+        <v>218</v>
+      </c>
       <c r="O50" s="178"/>
       <c r="P50" s="178" t="s">
         <v>146</v>
@@ -5872,9 +5949,6 @@
       <c r="Z51" s="117"/>
     </row>
     <row r="52" spans="5:26">
-      <c r="E52" s="46" t="s">
-        <v>156</v>
-      </c>
       <c r="O52" s="178"/>
       <c r="P52" s="178" t="s">
         <v>148</v>
@@ -5891,15 +5965,8 @@
       <c r="Z52" s="117"/>
     </row>
     <row r="53" spans="5:26">
-      <c r="E53" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F53" s="42">
-        <f>S26*10^3</f>
-        <v>75000</v>
-      </c>
-      <c r="G53" s="42" t="s">
-        <v>158</v>
+      <c r="E53" s="46" t="s">
+        <v>156</v>
       </c>
       <c r="O53" s="178"/>
       <c r="P53" s="178" t="s">
@@ -5918,14 +5985,14 @@
     </row>
     <row r="54" spans="5:26">
       <c r="E54" s="42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F54" s="42">
-        <f>R12</f>
-        <v>20.5</v>
+        <f>S26*10^3</f>
+        <v>75000</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="O54" s="178"/>
       <c r="P54" s="178" t="s">
@@ -5944,79 +6011,79 @@
     </row>
     <row r="55" spans="5:26">
       <c r="E55" s="42" t="s">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="F55" s="42">
-        <v>8000</v>
+        <f>R12</f>
+        <v>20.5</v>
       </c>
       <c r="G55" s="42" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="5:26">
       <c r="E56" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="42">
+        <v>8000</v>
+      </c>
+      <c r="G56" s="42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="5:26">
+      <c r="E57" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="42">
+      <c r="F57" s="42">
         <f>Q22</f>
         <v>25</v>
       </c>
-      <c r="G56" s="42" t="s">
+      <c r="G57" s="42" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="5:26">
-      <c r="E57" s="42" t="s">
+    <row r="58" spans="5:26">
+      <c r="E58" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="F57" s="120">
+      <c r="F58" s="120">
         <f>Q23</f>
         <v>2</v>
       </c>
-      <c r="G57" s="42" t="s">
+      <c r="G58" s="42" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="58" spans="5:26">
-      <c r="E58" s="42" t="s">
+    <row r="59" spans="5:26">
+      <c r="E59" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="F58" s="104">
+      <c r="F59" s="104">
         <f>1-Q21/52</f>
         <v>0.94230769230769229</v>
       </c>
     </row>
-    <row r="60" spans="5:26">
-      <c r="E60" s="42" t="s">
+    <row r="61" spans="5:26">
+      <c r="E61" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="183">
+      <c r="F61" s="183">
         <f>R25*R12*Q22*10^6</f>
         <v>871988000</v>
       </c>
-      <c r="G60" s="42" t="s">
+      <c r="G61" s="42" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="61" spans="5:26">
-      <c r="E61" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="F61" s="183">
-        <f>R28*R12*F55</f>
-        <v>2214849.5199999996</v>
-      </c>
-      <c r="G61" s="42" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="62" spans="5:26">
       <c r="E62" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F62" s="183">
-        <f>R29*R12*F55</f>
-        <v>732469.91999999993</v>
+        <f>R28*R12*F56</f>
+        <v>2214849.5199999996</v>
       </c>
       <c r="G62" s="42" t="s">
         <v>166</v>
@@ -6026,11 +6093,23 @@
       <c r="E63" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="F63" s="104">
-        <f>F62/F55</f>
+      <c r="F63" s="183">
+        <f>R29*R12*F56</f>
+        <v>732469.91999999993</v>
+      </c>
+      <c r="G63" s="42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="5:26">
+      <c r="E64" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F64" s="104">
+        <f>F63/F56</f>
         <v>91.558739999999986</v>
       </c>
-      <c r="G63" s="42" t="s">
+      <c r="G64" s="42" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6038,17 +6117,17 @@
       <c r="E79" s="46"/>
       <c r="N79" s="127"/>
       <c r="O79" s="128"/>
-      <c r="P79" s="203"/>
-      <c r="Q79" s="204"/>
-      <c r="R79" s="204"/>
-      <c r="S79" s="204"/>
-      <c r="T79" s="204"/>
-      <c r="U79" s="204"/>
-      <c r="V79" s="204"/>
-      <c r="W79" s="204"/>
-      <c r="X79" s="204"/>
-      <c r="Y79" s="204"/>
-      <c r="Z79" s="204"/>
+      <c r="P79" s="204"/>
+      <c r="Q79" s="205"/>
+      <c r="R79" s="205"/>
+      <c r="S79" s="205"/>
+      <c r="T79" s="205"/>
+      <c r="U79" s="205"/>
+      <c r="V79" s="205"/>
+      <c r="W79" s="205"/>
+      <c r="X79" s="205"/>
+      <c r="Y79" s="205"/>
+      <c r="Z79" s="205"/>
     </row>
     <row r="80" spans="5:26">
       <c r="N80" s="128"/>
